--- a/grillin.xlsx
+++ b/grillin.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cliff\Documents\1aaaaClasses\INFO4050\spring 2023\Week 11 - Trees and Random Forests\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cliff\Documents\1aaaaClasses\DSChunks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04AC0422-A0BE-42F5-B465-5F9F2E3BAACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B593772A-2C62-4836-B3CC-AFA43498A35E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{F2051E1C-02E8-4B6A-A35A-7901CF099D6E}"/>
+    <workbookView xWindow="28680" yWindow="2475" windowWidth="20640" windowHeight="11160" activeTab="2" xr2:uid="{F2051E1C-02E8-4B6A-A35A-7901CF099D6E}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
     <sheet name="Pivot Table" sheetId="4" r:id="rId2"/>
+    <sheet name="Gini Entropy" sheetId="5" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="33" r:id="rId3"/>
+    <pivotCache cacheId="12" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="20">
   <si>
     <t>forecast</t>
   </si>
@@ -84,10 +85,22 @@
     <t>Grand Total</t>
   </si>
   <si>
-    <t>(All)</t>
-  </si>
-  <si>
     <t>Count of grilled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini = </t>
+  </si>
+  <si>
+    <t>Gini</t>
+  </si>
+  <si>
+    <t>Entropy</t>
+  </si>
+  <si>
+    <t>Entropy =</t>
+  </si>
+  <si>
+    <t>Iris Dataset</t>
   </si>
 </sst>
 </file>
@@ -148,7 +161,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Cliff Whitworth" refreshedDate="45019.865686574078" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="30" xr:uid="{1C432778-4E9C-4E74-BDFA-30EA6B088648}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Cliff Whitworth" refreshedDate="45091.483344328706" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="30" xr:uid="{1C432778-4E9C-4E74-BDFA-30EA6B088648}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:D31" sheet="Data"/>
   </cacheSource>
@@ -374,7 +387,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EB34991C-D812-401B-9975-F894AFEAB9D3}" name="PivotTable3" cacheId="33" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EB34991C-D812-401B-9975-F894AFEAB9D3}" name="PivotTable3" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A5:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="3" colPageCount="1"/>
   <pivotFields count="4">
     <pivotField axis="axisPage" showAll="0">
@@ -426,9 +439,9 @@
     <i/>
   </colItems>
   <pageFields count="3">
-    <pageField fld="0" hier="-1"/>
-    <pageField fld="1" hier="-1"/>
-    <pageField fld="2" hier="-1"/>
+    <pageField fld="0" item="2" hier="-1"/>
+    <pageField fld="2" item="0" hier="-1"/>
+    <pageField fld="1" item="1" hier="-1"/>
   </pageFields>
   <dataFields count="1">
     <dataField name="Count of grilled" fld="3" subtotal="count" baseField="0" baseItem="0"/>
@@ -1189,8 +1202,8 @@
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="10.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.33203125" bestFit="1" customWidth="1"/>
@@ -1203,23 +1216,23 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -1227,7 +1240,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -1235,7 +1248,7 @@
         <v>7</v>
       </c>
       <c r="B6" s="3">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -1243,7 +1256,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -1251,7 +1264,86 @@
         <v>13</v>
       </c>
       <c r="B8" s="3">
-        <v>30</v>
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E89DB5A-1A29-4E9F-9A85-ABEDA4A07571}">
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <f>(40/120)^2</f>
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="C4">
+        <f>(41/120)^2</f>
+        <v>0.11673611111111111</v>
+      </c>
+      <c r="D4">
+        <f>(39/120)^2</f>
+        <v>0.10562500000000001</v>
+      </c>
+      <c r="E4">
+        <f>SUM(B4:D4)</f>
+        <v>0.33347222222222223</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6">
+        <f>1-E4</f>
+        <v>0.66652777777777783</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10">
+        <f>(40/120)*LOG(40/120, 2)</f>
+        <v>-0.52832083357371873</v>
+      </c>
+      <c r="C10">
+        <f>(41/120)*LOG(41/120, 2)</f>
+        <v>-0.52935735192173183</v>
+      </c>
+      <c r="D10">
+        <f>(39/120)*LOG(39/120, 2)</f>
+        <v>-0.52698372244253788</v>
+      </c>
+      <c r="E10">
+        <f>SUM(B10:D10)</f>
+        <v>-1.5846619079379884</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12">
+        <f>-1*E10</f>
+        <v>1.5846619079379884</v>
       </c>
     </row>
   </sheetData>

--- a/grillin.xlsx
+++ b/grillin.xlsx
@@ -1,25 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cliff\Documents\1aaaaClasses\DSChunks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cliff\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B593772A-2C62-4836-B3CC-AFA43498A35E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A42B79A-60D1-4A39-9C47-F7FE2518EFE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="2475" windowWidth="20640" windowHeight="11160" activeTab="2" xr2:uid="{F2051E1C-02E8-4B6A-A35A-7901CF099D6E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{F2051E1C-02E8-4B6A-A35A-7901CF099D6E}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
     <sheet name="Pivot Table" sheetId="4" r:id="rId2"/>
-    <sheet name="Gini Entropy" sheetId="5" r:id="rId3"/>
+    <sheet name="Math" sheetId="6" r:id="rId3"/>
+    <sheet name="Iris Gini Entropy" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="12" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="29">
   <si>
     <t>forecast</t>
   </si>
@@ -101,6 +102,33 @@
   </si>
   <si>
     <t>Iris Dataset</t>
+  </si>
+  <si>
+    <t>Gini 0: Pure</t>
+  </si>
+  <si>
+    <t>Gini .5: Equal Distribution</t>
+  </si>
+  <si>
+    <t>Gini 1: Random</t>
+  </si>
+  <si>
+    <t>Contains 1.6 bits of information</t>
+  </si>
+  <si>
+    <t>Entropy 1: High Level of Disorder</t>
+  </si>
+  <si>
+    <t>So Entropy is Between 0 and log base 2 k</t>
+  </si>
+  <si>
+    <t>Entropy 0: No Disorder</t>
+  </si>
+  <si>
+    <t>If p(x) = .5 (binary) then classes are equally distributed and entropy = 1</t>
+  </si>
+  <si>
+    <t>(All)</t>
   </si>
 </sst>
 </file>
@@ -387,10 +415,10 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EB34991C-D812-401B-9975-F894AFEAB9D3}" name="PivotTable3" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EB34991C-D812-401B-9975-F894AFEAB9D3}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A5:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="3" colPageCount="1"/>
   <pivotFields count="4">
-    <pivotField axis="axisPage" showAll="0">
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
       <items count="5">
         <item x="0"/>
         <item x="2"/>
@@ -439,9 +467,9 @@
     <i/>
   </colItems>
   <pageFields count="3">
-    <pageField fld="0" item="2" hier="-1"/>
-    <pageField fld="2" item="0" hier="-1"/>
-    <pageField fld="1" item="1" hier="-1"/>
+    <pageField fld="0" hier="-1"/>
+    <pageField fld="2" hier="-1"/>
+    <pageField fld="1" hier="-1"/>
   </pageFields>
   <dataFields count="1">
     <dataField name="Count of grilled" fld="3" subtotal="count" baseField="0" baseItem="0"/>
@@ -459,9 +487,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -499,7 +527,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -605,7 +633,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -747,7 +775,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1202,8 +1230,8 @@
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="10.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.33203125" bestFit="1" customWidth="1"/>
@@ -1216,7 +1244,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -1224,7 +1252,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -1232,7 +1260,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -1248,7 +1276,7 @@
         <v>7</v>
       </c>
       <c r="B6" s="3">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -1256,7 +1284,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -1264,7 +1292,7 @@
         <v>13</v>
       </c>
       <c r="B8" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1273,21 +1301,97 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E89DB5A-1A29-4E9F-9A85-ABEDA4A07571}">
-  <dimension ref="A1:E12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{824A009B-B01C-4234-9FD3-9BA9AC4365DE}">
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1">
+        <f>16/30</f>
+        <v>0.53333333333333333</v>
+      </c>
+      <c r="C1">
+        <f>14/30</f>
+        <v>0.46666666666666667</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <f>12/16</f>
+        <v>0.75</v>
+      </c>
+      <c r="C3">
+        <f>4/16</f>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <f>12/21</f>
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="C4">
+        <f>9/21</f>
+        <v>0.42857142857142855</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <f>10/16</f>
+        <v>0.625</v>
+      </c>
+      <c r="C5">
+        <f>6/16</f>
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <f>A1*A3*A4*A5</f>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="C7">
+        <f>C1*C3*C4*C5</f>
+        <v>1.8749999999999999E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B8">
+        <f>A7+C7</f>
+        <v>0.16160714285714284</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <f>A7/B8</f>
+        <v>0.88397790055248626</v>
+      </c>
+      <c r="C9">
+        <f>C7/B8</f>
+        <v>0.11602209944751382</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E89DB5A-1A29-4E9F-9A85-ABEDA4A07571}">
+  <dimension ref="A1:J15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B4">
         <f>(40/120)^2</f>
         <v>0.1111111111111111</v>
@@ -1304,8 +1408,16 @@
         <f>SUM(B4:D4)</f>
         <v>0.33347222222222223</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D6" t="s">
         <v>15</v>
       </c>
@@ -1313,13 +1425,16 @@
         <f>1-E4</f>
         <v>0.66652777777777783</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B10">
         <f>(40/120)*LOG(40/120, 2)</f>
         <v>-0.52832083357371873</v>
@@ -1336,14 +1451,41 @@
         <f>SUM(B10:D10)</f>
         <v>-1.5846619079379884</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D12" t="s">
         <v>18</v>
       </c>
       <c r="E12">
         <f>-1*E10</f>
         <v>1.5846619079379884</v>
+      </c>
+      <c r="G12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J14">
+        <f>LOG(3, 2)</f>
+        <v>1.5849625007211563</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G15" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
